--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ100"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10183,49 +10183,59 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>103714751</v>
+        <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>92869</v>
+        <v>93428</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, Uppsala, Upl</t>
+          <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>642786</v>
+        <v>642868</v>
       </c>
       <c r="R83" t="n">
-        <v>6638785</v>
+        <v>6638781</v>
       </c>
       <c r="S83" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10249,27 +10259,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Exkursion med Sveriges Mykologiska Förening.</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10278,43 +10273,39 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Äldre kalkgranskog med aspinslag</t>
+          <t>Kalkmarksgranskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103714751</t>
+          <t>https://artportalen.se/Sighting/137104523</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119821148</v>
+        <v>103714751</v>
       </c>
       <c r="B84" t="n">
-        <v>89894</v>
+        <v>92869</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10322,48 +10313,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5573</v>
+        <v>4769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Småskölding</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pluteus nanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, Upl</t>
+          <t>Herrhagsskogen, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>642779</v>
+        <v>642786</v>
       </c>
       <c r="R84" t="n">
-        <v>6638816</v>
+        <v>6638785</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10387,27 +10368,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Exkursion för Uppsala Svampklubb med Gillis Aronsson</t>
+          <t>Exkursion med Sveriges Mykologiska Förening.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10416,75 +10397,65 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Lövved, fuktigt liggande</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Lövved, fuktigt liggande</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Äldre kalkgranskog med aspinslag</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119821148</t>
+          <t>https://artportalen.se/Sighting/103714751</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>65724783</v>
+        <v>119821148</v>
       </c>
       <c r="B85" t="n">
-        <v>91443</v>
+        <v>89894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5754</v>
+        <v>5573</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Småskölding</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Pluteus nanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Pers. : Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10497,16 +10468,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Herrhagsskogen 3,5 km SO om Börje kyrka, Upl</t>
+          <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>642732</v>
+        <v>642779</v>
       </c>
       <c r="R85" t="n">
-        <v>6638882</v>
+        <v>6638816</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10533,17 +10506,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2007-08-21</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2007-08-21</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>2 ex. i äldre barrskog.</t>
+          <t>Exkursion för Uppsala Svampklubb med Gillis Aronsson</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10552,30 +10535,50 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Lövved, fuktigt liggande</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Lövved, fuktigt liggande</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65724783</t>
+          <t>https://artportalen.se/Sighting/119821148</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>95588964</v>
+        <v>65724783</v>
       </c>
       <c r="B86" t="n">
         <v>91443</v>
@@ -10605,7 +10608,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10613,18 +10616,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, Upl</t>
+          <t>Herrhagsskogen 3,5 km SO om Börje kyrka, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>642900</v>
+        <v>642732</v>
       </c>
       <c r="R86" t="n">
-        <v>6638796</v>
+        <v>6638882</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10651,17 +10652,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2007-08-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2007-08-21</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Svag bitter smak. Blir brunfärgad vid skrapning. Spormått ca 10-11 x 4-4,5 µm.</t>
+          <t>2 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10669,11 +10670,6 @@
       </c>
       <c r="AE86" t="b">
         <v>0</v>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG86" t="b">
         <v>0</v>
@@ -10681,24 +10677,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Samuel Persson, Jonathan Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95588964</t>
+          <t>https://artportalen.se/Sighting/65724783</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>96153533</v>
+        <v>95588964</v>
       </c>
       <c r="B87" t="n">
         <v>91443</v>
@@ -10726,21 +10722,31 @@
           <t>(Bres.) Corner</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Herrhagenskogen, Uppsala, Upl</t>
+          <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>642884</v>
+        <v>642900</v>
       </c>
       <c r="R87" t="n">
-        <v>6638805</v>
+        <v>6638796</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10764,22 +10770,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Svag bitter smak. Blir brunfärgad vid skrapning. Spormått ca 10-11 x 4-4,5 µm.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10787,6 +10788,11 @@
       </c>
       <c r="AE87" t="b">
         <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -10794,27 +10800,27 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Samuel Persson, Jonathan Persson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96153533</t>
+          <t>https://artportalen.se/Sighting/95588964</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>67446777</v>
+        <v>96153533</v>
       </c>
       <c r="B88" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10822,36 +10828,35 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, Upl</t>
+          <t>Herrhagenskogen, Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>642929</v>
+        <v>642884</v>
       </c>
       <c r="R88" t="n">
-        <v>6638866</v>
+        <v>6638805</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10878,22 +10883,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2017-09-05</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2017-09-05</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10902,34 +10907,33 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Patrick Fritzson</t>
+          <t>Annica Beil</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67446777</t>
+          <t>https://artportalen.se/Sighting/96153533</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>96371298</v>
+        <v>67446777</v>
       </c>
       <c r="B89" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10937,40 +10941,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>642965</v>
+        <v>642929</v>
       </c>
       <c r="R89" t="n">
-        <v>6638999</v>
+        <v>6638866</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10994,12 +10997,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2017-09-05</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2017-09-05</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11015,24 +11028,24 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Owe Rosengren, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96371298</t>
+          <t>https://artportalen.se/Sighting/67446777</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>96371342</v>
+        <v>96371298</v>
       </c>
       <c r="B90" t="n">
         <v>93235</v>
@@ -11070,10 +11083,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>642914</v>
+        <v>642965</v>
       </c>
       <c r="R90" t="n">
-        <v>6638984</v>
+        <v>6638999</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11132,50 +11145,42 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96371342</t>
+          <t>https://artportalen.se/Sighting/96371298</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>96141229</v>
+        <v>96371342</v>
       </c>
       <c r="B91" t="n">
-        <v>92567</v>
+        <v>93235</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -11184,10 +11189,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>642961</v>
+        <v>642914</v>
       </c>
       <c r="R91" t="n">
-        <v>6638995</v>
+        <v>6638984</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11214,12 +11219,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11246,13 +11251,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96141229</t>
+          <t>https://artportalen.se/Sighting/96371342</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>103479479</v>
+        <v>96141229</v>
       </c>
       <c r="B92" t="n">
         <v>92567</v>
@@ -11280,8 +11285,16 @@
           <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -11290,10 +11303,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>642977</v>
+        <v>642961</v>
       </c>
       <c r="R92" t="n">
-        <v>6638982</v>
+        <v>6638995</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11320,12 +11333,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11352,13 +11365,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103479479</t>
+          <t>https://artportalen.se/Sighting/96141229</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>103719924</v>
+        <v>103479479</v>
       </c>
       <c r="B93" t="n">
         <v>92567</v>
@@ -11387,19 +11400,22 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>642949</v>
+        <v>642977</v>
       </c>
       <c r="R93" t="n">
-        <v>6638972</v>
+        <v>6638982</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11423,12 +11439,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-09-10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11437,34 +11453,31 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Joachim Krumlinde, Lars-Inge Hedlund, Malin Löfgren, Maria Kroik, Mikaela Karlsson, Monica Andersson, Owe Rosengren, Samuel Persson, Per-Axel Karlsson, Tor Jonzon</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103719924</t>
+          <t>https://artportalen.se/Sighting/103479479</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128342486</v>
+        <v>103719924</v>
       </c>
       <c r="B94" t="n">
         <v>92567</v>
@@ -11492,31 +11505,20 @@
           <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>642933</v>
+        <v>642949</v>
       </c>
       <c r="R94" t="n">
-        <v>6638994</v>
+        <v>6638972</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11540,12 +11542,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11554,49 +11556,37 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Emil V. Nilsson, Joachim Krumlinde, Lars-Inge Hedlund, Malin Löfgren, Maria Kroik, Mikaela Karlsson, Monica Andersson, Owe Rosengren, Samuel Persson, Per-Axel Karlsson, Tor Jonzon</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128342486</t>
+          <t>https://artportalen.se/Sighting/103719924</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>67643581</v>
+        <v>128342486</v>
       </c>
       <c r="B95" t="n">
-        <v>101326</v>
+        <v>92567</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11604,37 +11594,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>6031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>S:ta Maria kyrka, 1,4 km NV-ut, Upl</t>
+          <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>642726</v>
+        <v>642933</v>
       </c>
       <c r="R95" t="n">
-        <v>6638942</v>
+        <v>6638994</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11661,12 +11659,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2017-09-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2017-09-16</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11675,74 +11673,87 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67643581</t>
+          <t>https://artportalen.se/Sighting/128342486</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>61269641</v>
+        <v>67643581</v>
       </c>
       <c r="B96" t="n">
-        <v>93194</v>
+        <v>101326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>239737</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Herrhagsskogen 3,5 km SO om Börje kyrka, Upl</t>
+          <t>S:ta Maria kyrka, 1,4 km NV-ut, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>642942</v>
+        <v>642726</v>
       </c>
       <c r="R96" t="n">
-        <v>6638992</v>
+        <v>6638942</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11769,17 +11780,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2017-09-16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>6 gyttringar i vegetationsskikt av kammossa, väggmossa, renlav och fönsterlav, på bergbunden mark.</t>
+          <t>2017-09-16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11788,36 +11794,34 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Karin Martinsson, Hans von Eichwald, Ulf Gärdenfors, Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61269641</t>
+          <t>https://artportalen.se/Sighting/67643581</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>61330236</v>
+        <v>61269641</v>
       </c>
       <c r="B97" t="n">
         <v>93194</v>
@@ -11846,16 +11850,18 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, Upl</t>
+          <t>Herrhagsskogen 3,5 km SO om Börje kyrka, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>642924</v>
+        <v>642942</v>
       </c>
       <c r="R97" t="n">
-        <v>6638989</v>
+        <v>6638992</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11892,7 +11898,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Exkursion med Uppsala Svampklubb. Ledare Gillis Aronsson</t>
+          <t>6 gyttringar i vegetationsskikt av kammossa, väggmossa, renlav och fönsterlav, på bergbunden mark.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11901,84 +11907,74 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Tor Jonzon, Ulf Gärdenfors, Åke Berg, Hans von Eichwald</t>
+          <t>Gillis Aronsson, Karin Martinsson, Hans von Eichwald, Ulf Gärdenfors, Mattias Lif</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61330236</t>
+          <t>https://artportalen.se/Sighting/61269641</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>73529212</v>
+        <v>61330236</v>
       </c>
       <c r="B98" t="n">
-        <v>91420</v>
+        <v>93194</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>256335</v>
+        <v>239737</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Herrhagsskogen 3,5 km SO om Börje kyrka, Upl</t>
+          <t>Herrhagsskogen, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>642859</v>
+        <v>642924</v>
       </c>
       <c r="R98" t="n">
-        <v>6638781</v>
+        <v>6638989</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12005,17 +12001,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
+          <t>2016-09-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
+          <t>2016-09-03</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>2 ex. i vegetationsskikt av husmossa, kransmossa, (skogs)viol och blåbärsris, under gran, asp och tall. På exkursion med Uppsala Svampklubb.</t>
+          <t>Exkursion med Uppsala Svampklubb. Ledare Gillis Aronsson</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12024,66 +12020,65 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Äldre barrskog med inslag av asp.</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Owe Rosengren, Tor Jonzon, Ulf Gärdenfors, Åke Berg, Hans von Eichwald</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73529212</t>
+          <t>https://artportalen.se/Sighting/61330236</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>111775251</v>
+        <v>73529212</v>
       </c>
       <c r="B99" t="n">
-        <v>91428</v>
+        <v>91420</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>256756</v>
+        <v>256335</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12091,16 +12086,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, SO om Börje kyrka, Upl</t>
+          <t>Herrhagsskogen 3,5 km SO om Börje kyrka, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>642748</v>
+        <v>642859</v>
       </c>
       <c r="R99" t="n">
-        <v>6639093</v>
+        <v>6638781</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12127,17 +12124,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>En häxring, 2 m i diameter, (ca. 10 ex.), i tätt, ungt granparti med inslag av tall.</t>
+          <t>2 ex. i vegetationsskikt av husmossa, kransmossa, (skogs)viol och blåbärsris, under gran, asp och tall. På exkursion med Uppsala Svampklubb.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12146,12 +12143,13 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Medelåldrig barrskog.</t>
+          <t>Äldre barrskog med inslag av asp.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12168,16 +12166,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111775251</t>
+          <t>https://artportalen.se/Sighting/73529212</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>96141240</v>
+        <v>111775251</v>
       </c>
       <c r="B100" t="n">
-        <v>92328</v>
+        <v>91428</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12185,37 +12183,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6040162</v>
+        <v>256756</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Herrhagsskogen, Upl</t>
+          <t>Herrhagsskogen, SO om Börje kyrka, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>642974</v>
+        <v>642748</v>
       </c>
       <c r="R100" t="n">
-        <v>6638896</v>
+        <v>6639093</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12242,12 +12246,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>En häxring, 2 m i diameter, (ca. 10 ex.), i tätt, ungt granparti med inslag av tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12256,43 +12265,153 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Medelåldrig barrskog.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111775251</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>96141240</v>
+      </c>
+      <c r="B101" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Herrhagsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>642974</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6638896</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Börje</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96141240</t>
         </is>
@@ -12399,6 +12518,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 2566-2020 artfynd.xlsx
+++ b/artfynd/S 2566-2020 artfynd.xlsx
@@ -10186,7 +10186,7 @@
         <v>137104523</v>
       </c>
       <c r="B83" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
